--- a/artfynd/A 46856-2023 artfynd.xlsx
+++ b/artfynd/A 46856-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46856-2023 artfynd.xlsx
+++ b/artfynd/A 46856-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114715996</v>
+        <v>114716003</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750555</v>
+        <v>750650</v>
       </c>
       <c r="R2" t="n">
-        <v>7428403</v>
+        <v>7428305</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,19 +773,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114716016</v>
+        <v>114716011</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750614</v>
+        <v>750296</v>
       </c>
       <c r="R3" t="n">
-        <v>7428095</v>
+        <v>7428471</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,19 +870,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114716015</v>
+        <v>114716013</v>
       </c>
       <c r="B4" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -919,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750613</v>
+        <v>750334</v>
       </c>
       <c r="R4" t="n">
-        <v>7428219</v>
+        <v>7428415</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,37 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114715994</v>
+        <v>114716014</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750309</v>
+        <v>750418</v>
       </c>
       <c r="R5" t="n">
-        <v>7428398</v>
+        <v>7428368</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1051,12 +1032,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,37 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114715997</v>
+        <v>114716015</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750553</v>
+        <v>750613</v>
       </c>
       <c r="R6" t="n">
-        <v>7428398</v>
+        <v>7428219</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1153,12 +1129,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,19 +1161,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114716013</v>
+        <v>114716016</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1225,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750334</v>
+        <v>750614</v>
       </c>
       <c r="R7" t="n">
-        <v>7428415</v>
+        <v>7428095</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,15 +1258,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114716011</v>
+        <v>114715994</v>
       </c>
       <c r="B8" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1269,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750296</v>
+        <v>750309</v>
       </c>
       <c r="R8" t="n">
-        <v>7428471</v>
+        <v>7428398</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1357,12 +1323,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,15 +1355,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114716014</v>
+        <v>114715996</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1366,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750418</v>
+        <v>750555</v>
       </c>
       <c r="R9" t="n">
-        <v>7428368</v>
+        <v>7428403</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1459,12 +1420,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,6 +1449,103 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114715997</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rudnevaare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>750553</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7428398</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46856-2023 artfynd.xlsx
+++ b/artfynd/A 46856-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114716003</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114716011</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114716013</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114716014</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114716015</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114716016</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114715994</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114715996</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,8 +1591,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114715997</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>